--- a/output_plant/stomataKonrad_Intermediate_moraweck_2019.xlsx
+++ b/output_plant/stomataKonrad_Intermediate_moraweck_2019.xlsx
@@ -537,7 +537,7 @@
     <t xml:space="preserve">generic value for angiosperms from Franks et al. (2014); 1 sigma error is 5% of mean</t>
   </si>
   <si>
-    <t xml:space="preserve">modified from the more elaborate Konrad model template to fit Franks model template; Pore length stored in GCLab (s1=1); pore depth stored in GCWab (s2=1). Density converted to m^-2; lengths to m; measured 2 sigma errors converted to 1 sigma.</t>
+    <t xml:space="preserve">Pore length stored in GCLab (s1=1); pore depth stored in GCWab (s2=1). Density converted to m^-2; lengths to m; measured 2 sigma errors converted to 1 sigma.</t>
   </si>
   <si>
     <t xml:space="preserve">Schleenhain-2o; Priabonian; Borna-Formation, Bruckdorf-Member; reticulosum</t>
